--- a/example_files/west_nile_metadata.xlsx
+++ b/example_files/west_nile_metadata.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chachen/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/theosanderson/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54EFCDCE-4000-BF43-987D-A40408C41EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FC7BEF-5ACA-2E43-A817-67B9A342CBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{8AA6C4E1-612A-6248-8120-629076D7CFF1}"/>
   </bookViews>
   <sheets>
     <sheet name="west_nile_metadata" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -208,9 +221,6 @@
     <t>tissue</t>
   </si>
   <si>
-    <t>test_WNV-1/Cyanocitta cristata /USA/03003243/2003</t>
-  </si>
-  <si>
     <t>KX547593</t>
   </si>
   <si>
@@ -278,6 +288,9 @@
   </si>
   <si>
     <t>Glendale</t>
+  </si>
+  <si>
+    <t>test_WNV-1/Cyanocitta_cristata /USA/03003243/2003</t>
   </si>
 </sst>
 </file>
@@ -1442,34 +1455,34 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
         <v>62</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>63</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>64</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>65</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
       </c>
       <c r="J9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" t="s">
         <v>68</v>
-      </c>
-      <c r="K9" t="s">
-        <v>69</v>
       </c>
       <c r="M9" s="1">
         <v>37892</v>
@@ -1477,10 +1490,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
         <v>70</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -1489,7 +1502,7 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
         <v>18</v>
@@ -1501,7 +1514,7 @@
         <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s">
         <v>20</v>
@@ -1515,19 +1528,19 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" t="s">
         <v>74</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
         <v>18</v>
@@ -1539,7 +1552,7 @@
         <v>19</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -1553,31 +1566,31 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>80</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>82</v>
-      </c>
-      <c r="F12" t="s">
-        <v>83</v>
       </c>
       <c r="G12" t="s">
         <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K12" t="s">
         <v>28</v>

--- a/example_files/west_nile_metadata.xlsx
+++ b/example_files/west_nile_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/theosanderson/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FC7BEF-5ACA-2E43-A817-67B9A342CBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9078FD81-C4B6-6048-BD67-9B55B9B9F043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{8AA6C4E1-612A-6248-8120-629076D7CFF1}"/>
   </bookViews>
@@ -290,7 +290,7 @@
     <t>Glendale</t>
   </si>
   <si>
-    <t>test_WNV-1/Cyanocitta_cristata /USA/03003243/2003</t>
+    <t>test_WNV-1/Cyanocitta_cristata/USA/03003243/2003</t>
   </si>
 </sst>
 </file>
@@ -1154,6 +1154,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC5AC95-285D-7643-A533-C3A9B14982C8}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="40.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">

--- a/example_files/west_nile_metadata.xlsx
+++ b/example_files/west_nile_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/theosanderson/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mverbies/projects/example_data/example_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9078FD81-C4B6-6048-BD67-9B55B9B9F043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50734963-929A-6649-B5A8-284047D79543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{8AA6C4E1-612A-6248-8120-629076D7CFF1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
   <si>
     <t>submissionId</t>
   </si>
@@ -65,9 +65,6 @@
     <t>geoLocCity</t>
   </si>
   <si>
-    <t>hostNameScientific</t>
-  </si>
-  <si>
     <t>anatomicalMaterial</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
     <t>Valey Center</t>
   </si>
   <si>
-    <t>Corvus brachyrhynchos</t>
-  </si>
-  <si>
     <t>tissue</t>
   </si>
   <si>
@@ -291,6 +285,9 @@
   </si>
   <si>
     <t>test_WNV-1/Cyanocitta_cristata/USA/03003243/2003</t>
+  </si>
+  <si>
+    <t>host</t>
   </si>
 </sst>
 </file>
@@ -1156,6 +1153,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
+    <col min="11" max="11" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -1190,39 +1188,39 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
       </c>
       <c r="M2" s="1">
         <v>40742</v>
@@ -1230,37 +1228,37 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="K3">
+        <v>7176</v>
+      </c>
+      <c r="L3" t="s">
         <v>28</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
       </c>
       <c r="M3" s="1">
         <v>40367</v>
@@ -1268,37 +1266,37 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>18</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>34</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
-      </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M4" s="1">
         <v>42548</v>
@@ -1306,37 +1304,37 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>38</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>39</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>40</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
         <v>41</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>18</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>42</v>
       </c>
-      <c r="I5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s">
-        <v>43</v>
-      </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M5" s="1">
         <v>41506</v>
@@ -1344,37 +1342,37 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
         <v>44</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>45</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
         <v>46</v>
       </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
         <v>47</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>18</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>48</v>
       </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>49</v>
       </c>
-      <c r="K6" t="s">
-        <v>50</v>
-      </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M6" s="1">
         <v>42933</v>
@@ -1382,37 +1380,37 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>52</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
         <v>53</v>
       </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
         <v>54</v>
       </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" t="s">
-        <v>55</v>
-      </c>
       <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" t="s">
         <v>28</v>
-      </c>
-      <c r="L7" t="s">
-        <v>29</v>
       </c>
       <c r="M7" s="1">
         <v>41943</v>
@@ -1420,37 +1418,37 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
         <v>56</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
         <v>57</v>
       </c>
-      <c r="C8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
         <v>58</v>
       </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8">
+        <v>85066</v>
+      </c>
+      <c r="L8" t="s">
         <v>59</v>
-      </c>
-      <c r="K8" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8" t="s">
-        <v>61</v>
       </c>
       <c r="M8" s="1">
         <v>39709</v>
@@ -1458,34 +1456,34 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s">
         <v>62</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F9" t="s">
         <v>63</v>
       </c>
-      <c r="D9" t="s">
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
         <v>64</v>
       </c>
-      <c r="F9" t="s">
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
         <v>65</v>
       </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="K9" t="s">
         <v>66</v>
-      </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" t="s">
-        <v>68</v>
       </c>
       <c r="M9" s="1">
         <v>37892</v>
@@ -1493,37 +1491,37 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
         <v>69</v>
       </c>
-      <c r="B10" t="s">
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
         <v>70</v>
       </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>19</v>
       </c>
-      <c r="J10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K10" t="s">
-        <v>20</v>
-      </c>
       <c r="L10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M10" s="1">
         <v>40402</v>
@@ -1531,37 +1529,37 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
         <v>73</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
         <v>74</v>
       </c>
-      <c r="C11" t="s">
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
         <v>75</v>
       </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" t="s">
-        <v>77</v>
-      </c>
-      <c r="K11" t="s">
-        <v>20</v>
+      <c r="K11">
+        <v>7177</v>
       </c>
       <c r="L11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M11" s="1">
         <v>42201</v>
@@ -1569,34 +1567,34 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
         <v>78</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>79</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
         <v>80</v>
       </c>
-      <c r="D12" t="s">
+      <c r="G12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" t="s">
         <v>81</v>
       </c>
-      <c r="F12" t="s">
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
         <v>82</v>
       </c>
-      <c r="G12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" t="s">
-        <v>83</v>
-      </c>
-      <c r="I12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" t="s">
-        <v>84</v>
-      </c>
       <c r="K12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M12" s="1">
         <v>40391</v>
